--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:23:56+00:00</t>
+    <t>2026-06-01T11:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:34:34+00:00</t>
+    <t>2026-06-02T13:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T13:07:12+00:00</t>
+    <t>2026-06-09T15:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:23:07+00:00</t>
+    <t>2026-06-10T09:53:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:53:12+00:00</t>
+    <t>2026-06-10T11:38:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T11:38:54+00:00</t>
+    <t>2026-06-12T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:35:19+00:00</t>
+    <t>2026-06-15T08:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:37:42+00:00</t>
+    <t>2026-06-15T17:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T17:37:50+00:00</t>
+    <t>2026-06-15T21:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T21:20:33+00:00</t>
+    <t>2026-06-16T10:30:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:30:24+00:00</t>
+    <t>2026-06-16T16:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:59:26+00:00</t>
+    <t>2026-06-17T13:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:25:59+00:00</t>
+    <t>2026-06-19T14:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:53:34+00:00</t>
+    <t>2026-06-22T08:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:46:55+00:00</t>
+    <t>2026-06-22T09:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:33:42+00:00</t>
+    <t>2026-06-26T11:41:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:41:48+00:00</t>
+    <t>2026-06-30T14:26:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:26:32+00:00</t>
+    <t>2026-07-01T15:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:59:29+00:00</t>
+    <t>2026-07-06T05:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T05:37:07+00:00</t>
+    <t>2026-07-06T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T12:58:40+00:00</t>
+    <t>2026-07-06T16:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T16:22:02+00:00</t>
+    <t>2026-07-08T18:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T18:47:08+00:00</t>
+    <t>2026-07-08T22:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T22:06:32+00:00</t>
+    <t>2026-07-09T09:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:27:37+00:00</t>
+    <t>2026-07-09T10:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T10:22:28+00:00</t>
+    <t>2026-07-09T13:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T13:13:16+00:00</t>
+    <t>2026-07-09T17:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T17:30:16+00:00</t>
+    <t>2026-07-10T13:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T13:02:50+00:00</t>
+    <t>2026-07-13T07:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T07:52:05+00:00</t>
+    <t>2026-07-14T09:15:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:15:46+00:00</t>
+    <t>2026-07-17T15:29:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T15:29:52+00:00</t>
+    <t>2026-07-27T22:31:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T22:31:32+00:00</t>
+    <t>2026-07-28T00:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:05:30+00:00</t>
+    <t>2026-07-29T17:39:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:39:31+00:00</t>
+    <t>2026-08-26T12:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:53:55+00:00</t>
+    <t>2026-08-27T15:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$31</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="238">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:34:15+00:00</t>
+    <t>2026-08-31T18:38:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -403,6 +403,25 @@
     <t>Timing.repeat.extension</t>
   </si>
   <si>
+    <t>Timing.repeat.extension:TimingDayOfMonth</t>
+  </si>
+  <si>
+    <t>TimingDayOfMonth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {timing-dayOfMonth}
+</t>
+  </si>
+  <si>
+    <t>Day of Month for schedule</t>
+  </si>
+  <si>
+    <t>When present, this extension indicates that the event actually only occurs on the specified days of the month, on the times as otherwise specified by the timing schedule.</t>
+  </si>
+  <si>
+    <t>The value must be an integer in thr range of 0 to 31. Its at the discretion of the implementer what to do if the value of the day is higher than the number of days in a given month.</t>
+  </si>
+  <si>
     <t>Timing.repeat.bounds[x]</t>
   </si>
   <si>
@@ -684,7 +703,10 @@
     <t>Timings are frequently determined by occurrences such as waking, eating and sleep.</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/elga-einnahmezeitpunkte</t>
+    <t>Real world event relating to the schedule.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/event-timing|4.0.1</t>
   </si>
   <si>
     <t>EIVL.event</t>
@@ -1056,12 +1078,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL30"/>
+  <dimension ref="A1:AL31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.78125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="28.5234375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.62109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.07421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1069,7 +1091,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="14.78515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="26.30078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1084,7 +1106,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="34.453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.90234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2076,14 +2098,16 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>124</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>125</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>21</v>
       </c>
@@ -2095,24 +2119,26 @@
         <v>85</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
@@ -2149,35 +2175,37 @@
         <v>21</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AC10" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>129</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" hidden="true">
@@ -2185,11 +2213,9 @@
         <v>130</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>131</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
@@ -2210,13 +2236,13 @@
         <v>104</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L11" t="s" s="2">
-        <v>126</v>
-      </c>
       <c r="M11" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2255,19 +2281,17 @@
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -2285,17 +2309,19 @@
         <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
       </c>
@@ -2313,16 +2339,16 @@
         <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2373,7 +2399,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2385,32 +2411,32 @@
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>90</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
@@ -2422,17 +2448,15 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>96</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
@@ -2469,31 +2493,31 @@
         <v>21</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>21</v>
@@ -2504,21 +2528,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>
@@ -2527,19 +2551,19 @@
         <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2577,45 +2601,45 @@
         <v>21</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>145</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2641,21 +2665,19 @@
         <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q15" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
         <v>21</v>
       </c>
@@ -2699,7 +2721,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2708,24 +2730,24 @@
         <v>85</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2748,68 +2770,68 @@
         <v>104</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q16" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="R16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="P16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -2818,24 +2840,24 @@
         <v>85</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2858,7 +2880,7 @@
         <v>104</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>163</v>
@@ -2866,8 +2888,12 @@
       <c r="M17" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+      <c r="N17" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>21</v>
       </c>
@@ -2915,7 +2941,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -2933,15 +2959,15 @@
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2964,20 +2990,16 @@
         <v>104</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O18" t="s" s="2">
         <v>170</v>
       </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
       </c>
@@ -3025,7 +3047,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3043,15 +3065,15 @@
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3074,7 +3096,7 @@
         <v>104</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>173</v>
@@ -3083,10 +3105,10 @@
         <v>174</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3135,7 +3157,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3153,15 +3175,15 @@
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3184,16 +3206,20 @@
         <v>104</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3217,13 +3243,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -3241,7 +3267,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -3259,15 +3285,15 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3290,48 +3316,46 @@
         <v>104</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q21" t="s" s="2">
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y21" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="R21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="Z21" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
@@ -3349,7 +3373,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3367,15 +3391,15 @@
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>171</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3398,20 +3422,22 @@
         <v>104</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q22" s="2"/>
+      <c r="Q22" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="R22" t="s" s="2">
         <v>21</v>
       </c>
@@ -3455,7 +3481,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3473,15 +3499,15 @@
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3495,7 +3521,7 @@
         <v>85</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
@@ -3504,13 +3530,13 @@
         <v>104</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3561,7 +3587,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -3579,15 +3605,15 @@
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="24" hidden="true">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3601,7 +3627,7 @@
         <v>85</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
@@ -3610,13 +3636,13 @@
         <v>104</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3667,7 +3693,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3685,15 +3711,15 @@
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3716,13 +3742,13 @@
         <v>104</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3749,29 +3775,31 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -3789,15 +3817,15 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3808,7 +3836,7 @@
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -3820,17 +3848,15 @@
         <v>104</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -3855,11 +3881,11 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -3877,13 +3903,13 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
@@ -3895,15 +3921,15 @@
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>90</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3926,7 +3952,7 @@
         <v>104</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>207</v>
@@ -3961,13 +3987,11 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -3985,7 +4009,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4006,12 +4030,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4025,7 +4049,7 @@
         <v>76</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
@@ -4034,20 +4058,18 @@
         <v>104</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>176</v>
+        <v>212</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -4071,11 +4093,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>215</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4093,7 +4117,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4111,15 +4135,15 @@
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>216</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4130,7 +4154,7 @@
         <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>104</v>
@@ -4142,16 +4166,20 @@
         <v>104</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -4175,13 +4203,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>21</v>
+        <v>221</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -4199,13 +4227,13 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
@@ -4217,15 +4245,15 @@
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="30" hidden="true">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4239,7 +4267,7 @@
         <v>85</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -4248,17 +4276,15 @@
         <v>104</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4283,13 +4309,13 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>228</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>229</v>
+        <v>21</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -4307,7 +4333,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4325,11 +4351,119 @@
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K31" t="s" s="2">
         <v>230</v>
       </c>
+      <c r="L31" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>237</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL30">
+  <autoFilter ref="A1:AL31">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -4339,7 +4473,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI29">
+  <conditionalFormatting sqref="A2:AI30">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T18:38:38+00:00</t>
+    <t>2026-09-03T18:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T18:40:45+00:00</t>
+    <t>2026-09-10T13:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
